--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.1.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="389">
   <si>
     <t xml:space="preserve">PDP Academy · Xadra filiali (1, 2 va 3-qavat): jami xarajatlar — yakuniy</t>
   </si>
@@ -589,18 +589,27 @@
     <t xml:space="preserve">E'tirof doskasi 1.8 × 1.0 m (brend panel, A4 akril cho'ntaklar — faxriylar, oy o'quvchisi nomzodlari)</t>
   </si>
   <si>
-    <t xml:space="preserve">Resepshn stoykasi 2.2 m (buyurtma: peshtaxta 1.10 m, old panelda logotip uchun joy)</t>
+    <t xml:space="preserve">Resepshn stoykasi 1.8 m (buyurtma: peshtaxta 1.10 m, zal tomonidagi panelda logotip uchun joy)</t>
   </si>
   <si>
     <t xml:space="preserve">TAXMIN — buyurtma asosida yasaladi</t>
   </si>
   <si>
+    <t xml:space="preserve">Resepshn to'siq panellari (past, L shaklida ~3.4 m) va xodim eshikchasi</t>
+  </si>
+  <si>
     <t xml:space="preserve">1-qavat: devordagi yorituvchi logotip ~1.5 m (to'q panelda)</t>
   </si>
   <si>
     <t xml:space="preserve">1-qavat: resepshn stoykasidagi logotip ~1.0 m (yoritilgan)</t>
   </si>
   <si>
+    <t xml:space="preserve">Turniketlar (buyurtmachida mavjud: kirish va chiqish)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyurtmachi: mavjud — narxi hisobga kirmaydi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kutilmagan xarajatlar</t>
   </si>
   <si>
@@ -709,7 +718,7 @@
     <t xml:space="preserve">• TAXMINIY narxlar (to'q sariq fon): sotuv va admin xonalari mebeli va interyeri, koridor doskalari, 1-qavat resepshn stoykasi, mehmonlar mebeli va logotiplari — Toshkent bozori bo'yicha dastlabki baho; mebelchi va reklama ustasi narxi bilan almashtiring. «Yakuniy» varag'ida taxminiy qism alohida ko'rsatilgan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Kirmagan: o'quv xonalari, ustozlar xonasi, call-markaz, CEO va koworking mebeli — mavjud; pol (kafel) va internet — mavjud; turniket — mavjud (o'rnatish, to'siq va evakuatsiya darvozasi alohida aniqlanadi); eshik furniturasi; shift va bo'yoq; ish haqi (agar narxga kirmagan bo'lsa).</t>
+    <t xml:space="preserve">• Kirmagan: o'quv xonalari, ustozlar xonasi, call-markaz, CEO va koworking mebeli — mavjud; pol (kafel) va internet — mavjud; turniketlar (2 ta) — mavjud (o'rnatish, to'siq va evakuatsiya darvozasi alohida aniqlanadi); eshik furniturasi; shift va bo'yoq; ish haqi (agar narxga kirmagan bo'lsa).</t>
   </si>
   <si>
     <t xml:space="preserve">Ranglar: ko'k — qo'lda kiritilgan qiymat; yashil — boshqa varaqdan olingan; qora — formula; sariq fon — o'zgartirish mumkin bo'lgan kataklar.</t>
@@ -739,15 +748,21 @@
     <t xml:space="preserve">Narx, $</t>
   </si>
   <si>
-    <t xml:space="preserve">Stoyka orqasidagi devorda yorituvchi logotip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resepshn stoykasining old panelidagi logotip</t>
+    <t xml:space="preserve">Resepshn orqasidagi o'ng devorda yorituvchi logotip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resepshn stoykasining zal tomonidagi panelidagi logotip</t>
   </si>
   <si>
     <t xml:space="preserve">Resepshn stoykasi (buyurtma asosida)</t>
   </si>
   <si>
+    <t xml:space="preserve">Resepshn to'siq panellari va xodim eshikchasi (L shaklida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">komplekt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resepshn xodimi kreslosi</t>
   </si>
   <si>
@@ -787,9 +802,6 @@
     <t xml:space="preserve">Lampalar (xona uchun)</t>
   </si>
   <si>
-    <t xml:space="preserve">komplekt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jami: 1-xona</t>
   </si>
   <si>
@@ -814,6 +826,9 @@
     <t xml:space="preserve">K1 koridori oxiridagi logotip devori (xona tomoni)</t>
   </si>
   <si>
+    <t xml:space="preserve">K1 koridori bilan orasidagi devor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Koridor uchidagi burchak ustunchasi</t>
   </si>
   <si>
@@ -865,9 +880,6 @@
     <t xml:space="preserve">Jami: 7-xona</t>
   </si>
   <si>
-    <t xml:space="preserve">K1 koridori bilan orasidagi devor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Admin (XZ2) bilan orasidagi devor</t>
   </si>
   <si>
@@ -977,9 +989,6 @@
   </si>
   <si>
     <t xml:space="preserve">Shisha ustidagi GKL (Call-markaz (XZ4) bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (4-xona bilan orasida)</t>
   </si>
   <si>
     <t xml:space="preserve">Eshik ustidagi GKL (1-xona eshigi)</t>
@@ -1899,15 +1908,15 @@
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
-        <v>5149.375</v>
+        <v>4991.25</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">C6*Narxlar!$C$19</f>
-        <v>61277562.5</v>
+        <v>59395875</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C6/$C$22)</f>
-        <v>0.0766671863531574</v>
+        <v>0.0738610847276704</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,15 +1928,15 @@
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
-        <v>5077.8</v>
+        <v>5146.8</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">C7*Narxlar!$C$19</f>
-        <v>60425820</v>
+        <v>61246920</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C7/$C$22)</f>
-        <v>0.0756015320041874</v>
+        <v>0.0761629313050586</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1947,7 +1956,7 @@
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C8/$C$22)</f>
-        <v>0.14001514498651</v>
+        <v>0.139163828410232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1967,7 +1976,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C9/$C$22)</f>
-        <v>0.122920605031031</v>
+        <v>0.122173226248264</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1987,7 +1996,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C10/$C$22)</f>
-        <v>0.0300154965773449</v>
+        <v>0.0298329971071342</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2007,7 +2016,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C11/$C$22)</f>
-        <v>0.0450232448660173</v>
+        <v>0.0447494956607013</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2027,7 +2036,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C12/$C$22)</f>
-        <v>0.0315490264123977</v>
+        <v>0.0313572028125086</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2047,7 +2056,7 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C13/$C$22)</f>
-        <v>0.0483880773196284</v>
+        <v>0.0480938693443383</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2067,7 +2076,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C14/$C$22)</f>
-        <v>0.00800733535476721</v>
+        <v>0.00795864935497777</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,7 +2096,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C15/$C$22)</f>
-        <v>0.0225206306852828</v>
+        <v>0.022383701310875</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2107,7 +2116,7 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C16/$C$22)</f>
-        <v>0.0067233466191688</v>
+        <v>0.00668246749551747</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2127,7 +2136,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C17/$C$22)</f>
-        <v>0.0505212815039844</v>
+        <v>0.0502141032740629</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2147,7 +2156,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C18/$C$22)</f>
-        <v>0.0185169630078992</v>
+        <v>0.0184043766333861</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,7 +2176,7 @@
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C19/$C$22)</f>
-        <v>0.223329587629054</v>
+        <v>0.221971704666177</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2179,15 +2188,15 @@
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
-        <v>5990</v>
+        <v>6490</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">C20*Narxlar!$C$19</f>
-        <v>71281000</v>
+        <v>77231000</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C20/$C$22)</f>
-        <v>0.089182948659869</v>
+        <v>0.0960397575522325</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,7 +2216,7 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C21/$C$22)</f>
-        <v>0.0110175929897</v>
+        <v>0.0109506040968647</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2217,11 +2226,11 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUM(C6:C21)</f>
-        <v>67165.3055882353</v>
+        <v>67576.1805882353</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">C22*Narxlar!$C$19</f>
-        <v>799267136.5</v>
+        <v>804156549</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -2231,16 +2240,16 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$68,"0%")&amp;")"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$70,"0%")&amp;")"</f>
         <v>Kutilmagan xarajatlar (10%)</v>
       </c>
       <c r="C23" s="17" t="n">
-        <f aca="false">C22*Narxlar!$C$68</f>
-        <v>6716.53055882353</v>
+        <f aca="false">C22*Narxlar!$C$70</f>
+        <v>6757.61805882353</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">C23*Narxlar!$C$19</f>
-        <v>79926713.65</v>
+        <v>80415654.9</v>
       </c>
       <c r="E23" s="16"/>
     </row>
@@ -2251,11 +2260,11 @@
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C22+C23</f>
-        <v>73881.8361470588</v>
+        <v>74333.7986470588</v>
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">C24*Narxlar!$C$19</f>
-        <v>879193850.15</v>
+        <v>884572203.9</v>
       </c>
       <c r="E24" s="20"/>
     </row>
@@ -2266,11 +2275,11 @@
       </c>
       <c r="C25" s="25" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
-        <v>7480</v>
+        <v>7980</v>
       </c>
       <c r="D25" s="26" t="n">
         <f aca="false">C25*Narxlar!$C$19</f>
-        <v>89012000</v>
+        <v>94962000</v>
       </c>
       <c r="E25" s="24"/>
     </row>
@@ -2305,15 +2314,15 @@
       </c>
       <c r="C29" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$7</f>
-        <v>2930</v>
+        <v>3430</v>
       </c>
       <c r="D29" s="8" t="n">
         <f aca="false">C29*Narxlar!$C$19</f>
-        <v>34867000</v>
+        <v>40817000</v>
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C29/$C$34)</f>
-        <v>0.0436237127835419</v>
+        <v>0.0507575298003325</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2325,15 +2334,15 @@
       </c>
       <c r="C30" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$17</f>
-        <v>19758.125</v>
+        <v>19634.5</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">C30*Narxlar!$C$19</f>
-        <v>235121687.5</v>
+        <v>233650550</v>
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C30/$C$34)</f>
-        <v>0.294171593904887</v>
+        <v>0.290553562351203</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2353,7 +2362,7 @@
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C31/$C$34)</f>
-        <v>0.160521565495393</v>
+        <v>0.159545566294953</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2365,15 +2374,15 @@
       </c>
       <c r="C32" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$34</f>
-        <v>26300.3957983193</v>
+        <v>26334.8957983193</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">C32*Narxlar!$C$19</f>
-        <v>312974710</v>
+        <v>313385260</v>
       </c>
       <c r="E32" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C32/$C$34)</f>
-        <v>0.391577103207971</v>
+        <v>0.389706780837272</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,7 +2402,7 @@
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C33/$C$34)</f>
-        <v>0.110106024608207</v>
+        <v>0.109436560716239</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2403,11 +2412,11 @@
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>67165.3055882353</v>
+        <v>67576.1805882353</v>
       </c>
       <c r="D34" s="13" t="n">
         <f aca="false">C34*Narxlar!$C$19</f>
-        <v>799267136.5</v>
+        <v>804156549</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">SUM(E29:E33)</f>
@@ -2646,7 +2655,7 @@
       </c>
       <c r="U6" s="32" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
-        <v>2180</v>
+        <v>2680</v>
       </c>
       <c r="V6" s="32" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
@@ -2654,7 +2663,7 @@
       </c>
       <c r="W6" s="34" t="n">
         <f aca="false">C6+E6+G6+I6+K6+L6+M6+N6+O6+P6+Q6+R6+S6+T6+U6+V6</f>
-        <v>2930</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2739,7 +2748,7 @@
       </c>
       <c r="U7" s="36" t="n">
         <f aca="false">SUM(U6:U6)</f>
-        <v>2180</v>
+        <v>2680</v>
       </c>
       <c r="V7" s="36" t="n">
         <f aca="false">SUM(V6:V6)</f>
@@ -2747,7 +2756,7 @@
       </c>
       <c r="W7" s="36" t="n">
         <f aca="false">SUM(W6:W6)</f>
-        <v>2930</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3062,19 +3071,19 @@
       </c>
       <c r="B13" s="31" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
-        <v>5.125</v>
+        <v>2.25</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
-        <v>281.875</v>
+        <v>123.75</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
-        <v>49.125</v>
+        <v>52</v>
       </c>
       <c r="E13" s="32" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
-        <v>589.5</v>
+        <v>624</v>
       </c>
       <c r="F13" s="31" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
@@ -3146,7 +3155,7 @@
       </c>
       <c r="W13" s="34" t="n">
         <f aca="false">C13+E13+G13+I13+K13+L13+M13+N13+O13+P13+Q13+R13+S13+T13+U13+V13</f>
-        <v>2852.575</v>
+        <v>2728.95</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3434,19 +3443,19 @@
       </c>
       <c r="B17" s="35" t="n">
         <f aca="false">SUM(B10:B16)</f>
-        <v>65.375</v>
+        <v>62.5</v>
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">SUM(C10:C16)</f>
-        <v>3595.625</v>
+        <v>3437.5</v>
       </c>
       <c r="D17" s="35" t="n">
         <f aca="false">SUM(D10:D16)</f>
-        <v>164.05</v>
+        <v>166.925</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">SUM(E10:E16)</f>
-        <v>1968.6</v>
+        <v>2003.1</v>
       </c>
       <c r="F17" s="35" t="n">
         <f aca="false">SUM(F10:F16)</f>
@@ -3518,7 +3527,7 @@
       </c>
       <c r="W17" s="36" t="n">
         <f aca="false">SUM(W10:W16)</f>
-        <v>19758.125</v>
+        <v>19634.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4147,11 +4156,11 @@
       </c>
       <c r="D28" s="31" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
-        <v>49.125</v>
+        <v>52</v>
       </c>
       <c r="E28" s="32" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
-        <v>589.5</v>
+        <v>624</v>
       </c>
       <c r="F28" s="31" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
@@ -4223,7 +4232,7 @@
       </c>
       <c r="W28" s="34" t="n">
         <f aca="false">C28+E28+G28+I28+K28+L28+M28+N28+O28+P28+Q28+R28+S28+T28+U28+V28</f>
-        <v>1295.5</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,11 +4714,11 @@
       </c>
       <c r="D34" s="35" t="n">
         <f aca="false">SUM(D28:D33)</f>
-        <v>117.95</v>
+        <v>120.825</v>
       </c>
       <c r="E34" s="36" t="n">
         <f aca="false">SUM(E28:E33)</f>
-        <v>1415.4</v>
+        <v>1449.9</v>
       </c>
       <c r="F34" s="35" t="n">
         <f aca="false">SUM(F28:F33)</f>
@@ -4781,7 +4790,7 @@
       </c>
       <c r="W34" s="36" t="n">
         <f aca="false">SUM(W28:W33)</f>
-        <v>26300.3957983193</v>
+        <v>26334.8957983193</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5096,19 +5105,19 @@
       </c>
       <c r="B41" s="38" t="n">
         <f aca="false">B7+B17+B25+B34+B39</f>
-        <v>93.625</v>
+        <v>90.75</v>
       </c>
       <c r="C41" s="39" t="n">
         <f aca="false">C7+C17+C25+C34+C39</f>
-        <v>5149.375</v>
+        <v>4991.25</v>
       </c>
       <c r="D41" s="38" t="n">
         <f aca="false">D7+D17+D25+D34+D39</f>
-        <v>423.15</v>
+        <v>428.9</v>
       </c>
       <c r="E41" s="39" t="n">
         <f aca="false">E7+E17+E25+E34+E39</f>
-        <v>5077.8</v>
+        <v>5146.8</v>
       </c>
       <c r="F41" s="38" t="n">
         <f aca="false">F7+F17+F25+F34+F39</f>
@@ -5172,7 +5181,7 @@
       </c>
       <c r="U41" s="39" t="n">
         <f aca="false">U7+U17+U25+U34+U39</f>
-        <v>5990</v>
+        <v>6490</v>
       </c>
       <c r="V41" s="39" t="n">
         <f aca="false">V7+V17+V25+V34+V39</f>
@@ -5180,12 +5189,12 @@
       </c>
       <c r="W41" s="39" t="n">
         <f aca="false">W7+W17+W25+W34+W39</f>
-        <v>67165.3055882353</v>
+        <v>67576.1805882353</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$68,"0%")&amp;" — «Narxlar» varag'idan)"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$70,"0%")&amp;" — «Narxlar» varag'idan)"</f>
         <v>Kutilmagan xarajatlar (10% — «Narxlar» varag'idan)</v>
       </c>
       <c r="B42" s="16"/>
@@ -5210,8 +5219,8 @@
       <c r="U42" s="16"/>
       <c r="V42" s="16"/>
       <c r="W42" s="41" t="n">
-        <f aca="false">W41*Narxlar!$C$68</f>
-        <v>6716.53055882353</v>
+        <f aca="false">W41*Narxlar!$C$70</f>
+        <v>6757.61805882353</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,7 +5250,7 @@
       <c r="V43" s="20"/>
       <c r="W43" s="39" t="n">
         <f aca="false">W41+W42</f>
-        <v>73881.8361470588</v>
+        <v>74333.7986470588</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,7 +5280,7 @@
       <c r="V44" s="20"/>
       <c r="W44" s="22" t="n">
         <f aca="false">W43*Narxlar!$C$19</f>
-        <v>879193850.15</v>
+        <v>884572203.9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5304,7 +5313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6389,7 +6398,7 @@
         <v>500</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>179</v>
@@ -6403,7 +6412,7 @@
         <v>191</v>
       </c>
       <c r="C67" s="46" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>100</v>
@@ -6419,14 +6428,14 @@
       <c r="B68" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C68" s="47" t="n">
-        <v>0.1</v>
+      <c r="C68" s="46" t="n">
+        <v>250</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6434,16 +6443,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C69" s="43" t="n">
-        <v>3.5</v>
+        <v>193</v>
+      </c>
+      <c r="C69" s="44" t="n">
+        <v>2</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6451,16 +6460,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C70" s="47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="C70" s="43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6470,9 +6479,8 @@
       <c r="B71" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C71" s="48" t="n">
-        <f aca="false">C69-C70</f>
-        <v>1</v>
+      <c r="C71" s="43" t="n">
+        <v>3.5</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>104</v>
@@ -6489,13 +6497,13 @@
         <v>200</v>
       </c>
       <c r="C72" s="43" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6503,17 +6511,17 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C73" s="48" t="n">
-        <f aca="false">C69-C72</f>
-        <v>1.4</v>
+        <f aca="false">C71-C72</f>
+        <v>1</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6521,16 +6529,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C74" s="43" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6538,17 +6546,17 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C75" s="49" t="n">
-        <f aca="false">C69</f>
-        <v>3.5</v>
+        <v>205</v>
+      </c>
+      <c r="C75" s="48" t="n">
+        <f aca="false">C71-C74</f>
+        <v>1.4</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6556,121 +6564,156 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C76" s="43" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" s="49" t="n">
+        <f aca="false">C71</f>
+        <v>3.5</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C78" s="43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="2" t="s">
-        <v>211</v>
+      <c r="B80" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -6705,12 +6748,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6721,25 +6764,25 @@
         <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>94</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>5</v>
@@ -6770,7 +6813,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="51"/>
@@ -6781,7 +6824,7 @@
         <v>113</v>
       </c>
       <c r="I6" s="7" t="n">
-        <f aca="false">Narxlar!$C$66</f>
+        <f aca="false">Narxlar!$C$67</f>
         <v>500</v>
       </c>
       <c r="J6" s="53" t="n">
@@ -6800,7 +6843,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E7" s="50"/>
       <c r="F7" s="51"/>
@@ -6811,7 +6854,7 @@
         <v>113</v>
       </c>
       <c r="I7" s="7" t="n">
-        <f aca="false">Narxlar!$C$67</f>
+        <f aca="false">Narxlar!$C$68</f>
         <v>250</v>
       </c>
       <c r="J7" s="53" t="n">
@@ -6830,7 +6873,7 @@
         <v>22</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="51"/>
@@ -6860,7 +6903,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E9" s="50"/>
       <c r="F9" s="51"/>
@@ -6868,15 +6911,15 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>113</v>
+        <v>245</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">Narxlar!$C$56</f>
-        <v>130</v>
+        <f aca="false">Narxlar!$C$66</f>
+        <v>500</v>
       </c>
       <c r="J9" s="53" t="n">
         <f aca="false">G9*I9</f>
-        <v>130</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,7 +6933,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="51"/>
@@ -6901,12 +6944,12 @@
         <v>113</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">Narxlar!$C$58</f>
-        <v>450</v>
+        <f aca="false">Narxlar!$C$56</f>
+        <v>130</v>
       </c>
       <c r="J10" s="53" t="n">
         <f aca="false">G10*I10</f>
-        <v>450</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6920,7 +6963,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="E11" s="50"/>
       <c r="F11" s="51"/>
@@ -6931,80 +6974,74 @@
         <v>113</v>
       </c>
       <c r="I11" s="7" t="n">
+        <f aca="false">Narxlar!$C$58</f>
+        <v>450</v>
+      </c>
+      <c r="J11" s="53" t="n">
+        <f aca="false">G11*I11</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <f aca="false">Narxlar!$C$60</f>
         <v>100</v>
       </c>
-      <c r="J11" s="53" t="n">
-        <f aca="false">G11*I11</f>
+      <c r="J12" s="53" t="n">
+        <f aca="false">G12*I12</f>
         <v>100</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="12" t="n">
-        <f aca="false">SUM(J6:J11)</f>
-        <v>2930</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="12" t="n">
+        <f aca="false">SUM(J6:J12)</f>
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
-        <v>2.5</v>
-      </c>
-      <c r="G15" s="51" t="n">
-        <f aca="false">E15*F15</f>
-        <v>11.5</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
-      </c>
-      <c r="J15" s="53" t="n">
-        <f aca="false">G15*I15</f>
-        <v>632.5</v>
-      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
@@ -7017,19 +7054,18 @@
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
+        <v>249</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>4.6</v>
       </c>
       <c r="F16" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G16" s="51" t="n">
         <f aca="false">E16*F16</f>
-        <v>2.25</v>
+        <v>11.5</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>157</v>
@@ -7040,7 +7076,7 @@
       </c>
       <c r="J16" s="53" t="n">
         <f aca="false">G16*I16</f>
-        <v>123.75</v>
+        <v>632.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7051,32 +7087,33 @@
         <v>63</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>0.3</v>
+        <v>250</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F17" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$72</f>
+        <v>2.5</v>
       </c>
       <c r="G17" s="51" t="n">
         <f aca="false">E17*F17</f>
-        <v>1.05</v>
+        <v>2.25</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
       </c>
       <c r="J17" s="53" t="n">
         <f aca="false">G17*I17</f>
-        <v>12.6</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7090,18 +7127,18 @@
         <v>9</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E18" s="50" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G18" s="51" t="n">
         <f aca="false">E18*F18</f>
-        <v>4.6</v>
+        <v>1.05</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>157</v>
@@ -7112,7 +7149,7 @@
       </c>
       <c r="J18" s="53" t="n">
         <f aca="false">G18*I18</f>
-        <v>55.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7126,18 +7163,18 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E19" s="50" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="F19" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$73</f>
+        <v>1</v>
       </c>
       <c r="G19" s="51" t="n">
         <f aca="false">E19*F19</f>
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>157</v>
@@ -7148,7 +7185,7 @@
       </c>
       <c r="J19" s="53" t="n">
         <f aca="false">G19*I19</f>
-        <v>8.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7162,19 +7199,18 @@
         <v>9</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E20" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
+        <v>253</v>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>0.2</v>
       </c>
       <c r="F20" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G20" s="51" t="n">
         <f aca="false">E20*F20</f>
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>157</v>
@@ -7185,7 +7221,7 @@
       </c>
       <c r="J20" s="53" t="n">
         <f aca="false">G20*I20</f>
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7196,32 +7232,33 @@
         <v>63</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E21" s="50" t="n">
-        <v>7.7</v>
+        <v>254</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F21" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$73</f>
+        <v>1</v>
       </c>
       <c r="G21" s="51" t="n">
         <f aca="false">E21*F21</f>
-        <v>26.95</v>
+        <v>0.9</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I21" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J21" s="53" t="n">
         <f aca="false">G21*I21</f>
-        <v>417.725</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7235,13 +7272,13 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G22" s="51" t="n">
@@ -7268,26 +7305,32 @@
         <v>63</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="52" t="n">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="E23" s="50" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="51" t="n">
+        <f aca="false">E23*F23</f>
+        <v>26.95</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I23" s="7" t="n">
-        <f aca="false">Narxlar!$C$8</f>
-        <v>1032</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J23" s="53" t="n">
         <f aca="false">G23*I23</f>
-        <v>1032</v>
+        <v>417.725</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7298,10 +7341,10 @@
         <v>63</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E24" s="50"/>
       <c r="F24" s="51"/>
@@ -7309,83 +7352,77 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="I24" s="7" t="n">
+        <f aca="false">Narxlar!$C$8</f>
+        <v>1032</v>
+      </c>
+      <c r="J24" s="53" t="n">
+        <f aca="false">G24*I24</f>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" s="50"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I25" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
         <v>168</v>
       </c>
-      <c r="J24" s="53" t="n">
-        <f aca="false">G24*I24</f>
+      <c r="J25" s="53" t="n">
+        <f aca="false">G25*I25</f>
         <v>168</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="12" t="n">
-        <f aca="false">SUM(J15:J24)</f>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="12" t="n">
+        <f aca="false">SUM(J16:J25)</f>
         <v>2878.7</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E28" s="50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F28" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
-        <v>2.5</v>
-      </c>
-      <c r="G28" s="51" t="n">
-        <f aca="false">E28*F28</f>
-        <v>11.75</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
-      </c>
-      <c r="J28" s="53" t="n">
-        <f aca="false">G28*I28</f>
-        <v>646.25</v>
-      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
@@ -7398,19 +7435,18 @@
         <v>8</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E29" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
+        <v>249</v>
+      </c>
+      <c r="E29" s="50" t="n">
+        <v>4.7</v>
       </c>
       <c r="F29" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G29" s="51" t="n">
         <f aca="false">E29*F29</f>
-        <v>2.25</v>
+        <v>11.75</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>157</v>
@@ -7421,7 +7457,7 @@
       </c>
       <c r="J29" s="53" t="n">
         <f aca="false">G29*I29</f>
-        <v>123.75</v>
+        <v>646.25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7432,32 +7468,33 @@
         <v>64</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="E30" s="50" t="n">
-        <v>4.7</v>
+        <v>250</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F30" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <f aca="false">Narxlar!$C$72</f>
+        <v>2.5</v>
       </c>
       <c r="G30" s="51" t="n">
         <f aca="false">E30*F30</f>
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I30" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
       </c>
       <c r="J30" s="53" t="n">
         <f aca="false">G30*I30</f>
-        <v>56.4</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7471,18 +7508,18 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E31" s="50" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="F31" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$73</f>
+        <v>1</v>
       </c>
       <c r="G31" s="51" t="n">
         <f aca="false">E31*F31</f>
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>157</v>
@@ -7493,7 +7530,7 @@
       </c>
       <c r="J31" s="53" t="n">
         <f aca="false">G31*I31</f>
-        <v>8.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7507,19 +7544,18 @@
         <v>9</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E32" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
+        <v>253</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>0.2</v>
       </c>
       <c r="F32" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G32" s="51" t="n">
         <f aca="false">E32*F32</f>
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>157</v>
@@ -7530,7 +7566,7 @@
       </c>
       <c r="J32" s="53" t="n">
         <f aca="false">G32*I32</f>
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7541,32 +7577,33 @@
         <v>64</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E33" s="50" t="n">
-        <v>7.7</v>
+        <v>254</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F33" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$73</f>
+        <v>1</v>
       </c>
       <c r="G33" s="51" t="n">
         <f aca="false">E33*F33</f>
-        <v>26.95</v>
+        <v>0.9</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I33" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J33" s="53" t="n">
         <f aca="false">G33*I33</f>
-        <v>417.725</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7580,13 +7617,13 @@
         <v>10</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E34" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F34" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G34" s="51" t="n">
@@ -7613,26 +7650,32 @@
         <v>64</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E35" s="50"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="52" t="n">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="E35" s="50" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F35" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G35" s="51" t="n">
+        <f aca="false">E35*F35</f>
+        <v>26.95</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I35" s="7" t="n">
-        <f aca="false">Narxlar!$C$8</f>
-        <v>1032</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J35" s="53" t="n">
         <f aca="false">G35*I35</f>
-        <v>1032</v>
+        <v>417.725</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7643,10 +7686,10 @@
         <v>64</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E36" s="50"/>
       <c r="F36" s="51"/>
@@ -7654,84 +7697,77 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="I36" s="7" t="n">
+        <f aca="false">Narxlar!$C$8</f>
+        <v>1032</v>
+      </c>
+      <c r="J36" s="53" t="n">
+        <f aca="false">G36*I36</f>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E37" s="50"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I37" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
         <v>168</v>
       </c>
-      <c r="J36" s="53" t="n">
-        <f aca="false">G36*I36</f>
+      <c r="J37" s="53" t="n">
+        <f aca="false">G37*I37</f>
         <v>168</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="12" t="n">
-        <f aca="false">SUM(J28:J36)</f>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="12" t="n">
+        <f aca="false">SUM(J29:J37)</f>
         <v>2881.05</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
-      </c>
-      <c r="F40" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
-        <v>2.5</v>
-      </c>
-      <c r="G40" s="51" t="n">
-        <f aca="false">E40*F40</f>
-        <v>2.25</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
-      </c>
-      <c r="J40" s="53" t="n">
-        <f aca="false">G40*I40</f>
-        <v>123.75</v>
-      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
@@ -7741,32 +7777,33 @@
         <v>65</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E41" s="50" t="n">
-        <v>0.15</v>
+        <v>250</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F41" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$72</f>
+        <v>2.5</v>
       </c>
       <c r="G41" s="51" t="n">
         <f aca="false">E41*F41</f>
-        <v>0.525</v>
+        <v>2.25</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I41" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
       </c>
       <c r="J41" s="53" t="n">
         <f aca="false">G41*I41</f>
-        <v>6.3</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7780,18 +7817,18 @@
         <v>9</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E42" s="50" t="n">
-        <v>4.7</v>
+        <v>0.15</v>
       </c>
       <c r="F42" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G42" s="51" t="n">
         <f aca="false">E42*F42</f>
-        <v>16.45</v>
+        <v>0.525</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>157</v>
@@ -7802,7 +7839,7 @@
       </c>
       <c r="J42" s="53" t="n">
         <f aca="false">G42*I42</f>
-        <v>197.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7816,19 +7853,18 @@
         <v>9</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E43" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
+        <v>261</v>
+      </c>
+      <c r="E43" s="50" t="n">
+        <v>4.7</v>
       </c>
       <c r="F43" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G43" s="51" t="n">
         <f aca="false">E43*F43</f>
-        <v>0.9</v>
+        <v>16.45</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>157</v>
@@ -7839,7 +7875,7 @@
       </c>
       <c r="J43" s="53" t="n">
         <f aca="false">G43*I43</f>
-        <v>10.8</v>
+        <v>197.4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7850,32 +7886,33 @@
         <v>65</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E44" s="50" t="n">
-        <v>7.7</v>
+        <v>254</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
       </c>
       <c r="F44" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$73</f>
+        <v>1</v>
       </c>
       <c r="G44" s="51" t="n">
         <f aca="false">E44*F44</f>
-        <v>26.95</v>
+        <v>0.9</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>157</v>
       </c>
       <c r="I44" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J44" s="53" t="n">
         <f aca="false">G44*I44</f>
-        <v>417.725</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7889,13 +7926,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E45" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F45" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G45" s="51" t="n">
@@ -7922,26 +7959,32 @@
         <v>65</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E46" s="50"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="52" t="n">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="E46" s="50" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F46" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G46" s="51" t="n">
+        <f aca="false">E46*F46</f>
+        <v>26.95</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I46" s="7" t="n">
-        <f aca="false">Narxlar!$C$8</f>
-        <v>1032</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J46" s="53" t="n">
         <f aca="false">G46*I46</f>
-        <v>1032</v>
+        <v>417.725</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7952,10 +7995,10 @@
         <v>65</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E47" s="50"/>
       <c r="F47" s="51"/>
@@ -7963,83 +8006,77 @@
         <v>1</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="I47" s="7" t="n">
+        <f aca="false">Narxlar!$C$8</f>
+        <v>1032</v>
+      </c>
+      <c r="J47" s="53" t="n">
+        <f aca="false">G47*I47</f>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" s="50"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I48" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
         <v>168</v>
       </c>
-      <c r="J47" s="53" t="n">
-        <f aca="false">G47*I47</f>
+      <c r="J48" s="53" t="n">
+        <f aca="false">G48*I48</f>
         <v>168</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="54"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="54"/>
-      <c r="D48" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="12" t="n">
-        <f aca="false">SUM(J40:J47)</f>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="12" t="n">
+        <f aca="false">SUM(J41:J48)</f>
         <v>2373.7</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="29" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" s="50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F51" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
-        <v>2.5</v>
-      </c>
-      <c r="G51" s="51" t="n">
-        <f aca="false">E51*F51</f>
-        <v>2.875</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
-      </c>
-      <c r="J51" s="53" t="n">
-        <f aca="false">G51*I51</f>
-        <v>158.125</v>
-      </c>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
@@ -8052,14 +8089,14 @@
         <v>8</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E52" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F52" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G52" s="51" t="n">
@@ -8089,13 +8126,13 @@
         <v>9</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E53" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G53" s="51" t="n">
@@ -8125,13 +8162,13 @@
         <v>9</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E54" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F54" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G54" s="51" t="n">
@@ -8161,13 +8198,13 @@
         <v>9</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E55" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F55" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G55" s="51" t="n">
@@ -8197,18 +8234,18 @@
         <v>9</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="E56" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F56" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G56" s="51" t="n">
         <f aca="false">E56*F56</f>
-        <v>1.15</v>
+        <v>4.025</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>157</v>
@@ -8219,7 +8256,7 @@
       </c>
       <c r="J56" s="53" t="n">
         <f aca="false">G56*I56</f>
-        <v>13.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8233,13 +8270,13 @@
         <v>9</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E57" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F57" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G57" s="51" t="n">
@@ -8269,13 +8306,13 @@
         <v>9</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E58" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F58" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G58" s="51" t="n">
@@ -8305,13 +8342,13 @@
         <v>9</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E59" s="50" t="n">
         <v>0.25</v>
       </c>
       <c r="F59" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G59" s="51" t="n">
@@ -8341,13 +8378,13 @@
         <v>9</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E60" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F60" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G60" s="51" t="n">
@@ -8377,13 +8414,13 @@
         <v>9</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E61" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F61" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G61" s="51" t="n">
@@ -8413,14 +8450,14 @@
         <v>9</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E62" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F62" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G62" s="51" t="n">
@@ -8450,13 +8487,13 @@
         <v>10</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>8.8</v>
       </c>
       <c r="F63" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G63" s="51" t="n">
@@ -8486,13 +8523,13 @@
         <v>10</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E64" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F64" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G64" s="51" t="n">
@@ -8522,7 +8559,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E65" s="50"/>
       <c r="F65" s="51"/>
@@ -8552,7 +8589,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E66" s="50"/>
       <c r="F66" s="51"/>
@@ -8560,7 +8597,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I66" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8576,7 +8613,7 @@
       <c r="B67" s="54"/>
       <c r="C67" s="54"/>
       <c r="D67" s="11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E67" s="54"/>
       <c r="F67" s="54"/>
@@ -8584,8 +8621,8 @@
       <c r="H67" s="54"/>
       <c r="I67" s="54"/>
       <c r="J67" s="12" t="n">
-        <f aca="false">SUM(J51:J66)</f>
-        <v>2852.575</v>
+        <f aca="false">SUM(J52:J66)</f>
+        <v>2728.95</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8613,14 +8650,14 @@
         <v>8</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E70" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F70" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G70" s="51" t="n">
@@ -8650,13 +8687,13 @@
         <v>9</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E71" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F71" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G71" s="51" t="n">
@@ -8686,13 +8723,13 @@
         <v>9</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E72" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F72" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G72" s="51" t="n">
@@ -8722,13 +8759,13 @@
         <v>9</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E73" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F73" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G73" s="51" t="n">
@@ -8758,14 +8795,14 @@
         <v>9</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E74" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F74" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G74" s="51" t="n">
@@ -8795,13 +8832,13 @@
         <v>10</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E75" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F75" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G75" s="51" t="n">
@@ -8831,13 +8868,13 @@
         <v>10</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E76" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F76" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G76" s="51" t="n">
@@ -8867,7 +8904,7 @@
         <v>11</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E77" s="50"/>
       <c r="F77" s="51"/>
@@ -8897,7 +8934,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E78" s="50"/>
       <c r="F78" s="51"/>
@@ -8905,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I78" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8921,7 +8958,7 @@
       <c r="B79" s="54"/>
       <c r="C79" s="54"/>
       <c r="D79" s="11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E79" s="54"/>
       <c r="F79" s="54"/>
@@ -8958,13 +8995,13 @@
         <v>8</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E82" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F82" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G82" s="51" t="n">
@@ -8994,14 +9031,14 @@
         <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E83" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F83" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G83" s="51" t="n">
@@ -9031,13 +9068,13 @@
         <v>9</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E84" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F84" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G84" s="51" t="n">
@@ -9067,13 +9104,13 @@
         <v>9</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E85" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F85" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G85" s="51" t="n">
@@ -9103,13 +9140,13 @@
         <v>9</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E86" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F86" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G86" s="51" t="n">
@@ -9139,13 +9176,13 @@
         <v>9</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E87" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F87" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G87" s="51" t="n">
@@ -9175,14 +9212,14 @@
         <v>9</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E88" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F88" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G88" s="51" t="n">
@@ -9212,13 +9249,13 @@
         <v>10</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E89" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F89" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G89" s="51" t="n">
@@ -9248,13 +9285,13 @@
         <v>10</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E90" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F90" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G90" s="51" t="n">
@@ -9284,7 +9321,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E91" s="50"/>
       <c r="F91" s="51"/>
@@ -9314,7 +9351,7 @@
         <v>13</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E92" s="50"/>
       <c r="F92" s="51"/>
@@ -9322,7 +9359,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I92" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9338,7 +9375,7 @@
       <c r="B93" s="54"/>
       <c r="C93" s="54"/>
       <c r="D93" s="11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -9375,13 +9412,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E96" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F96" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G96" s="51" t="n">
@@ -9411,14 +9448,14 @@
         <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E97" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F97" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G97" s="51" t="n">
@@ -9448,13 +9485,13 @@
         <v>9</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E98" s="50" t="n">
         <v>1.55</v>
       </c>
       <c r="F98" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G98" s="51" t="n">
@@ -9484,13 +9521,13 @@
         <v>9</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E99" s="50" t="n">
         <v>2.6</v>
       </c>
       <c r="F99" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G99" s="51" t="n">
@@ -9520,13 +9557,13 @@
         <v>9</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E100" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F100" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G100" s="51" t="n">
@@ -9556,13 +9593,13 @@
         <v>9</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E101" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F101" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G101" s="51" t="n">
@@ -9592,13 +9629,13 @@
         <v>9</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E102" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F102" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G102" s="51" t="n">
@@ -9628,14 +9665,14 @@
         <v>9</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E103" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F103" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G103" s="51" t="n">
@@ -9665,13 +9702,13 @@
         <v>10</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E104" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F104" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G104" s="51" t="n">
@@ -9701,13 +9738,13 @@
         <v>10</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E105" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F105" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G105" s="51" t="n">
@@ -9737,7 +9774,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E106" s="50"/>
       <c r="F106" s="51"/>
@@ -9767,7 +9804,7 @@
         <v>13</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E107" s="50"/>
       <c r="F107" s="51"/>
@@ -9775,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I107" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9791,7 +9828,7 @@
       <c r="B108" s="54"/>
       <c r="C108" s="54"/>
       <c r="D108" s="11" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E108" s="54"/>
       <c r="F108" s="54"/>
@@ -9828,13 +9865,13 @@
         <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E111" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F111" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G111" s="51" t="n">
@@ -9864,13 +9901,13 @@
         <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E112" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F112" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G112" s="51" t="n">
@@ -9900,14 +9937,14 @@
         <v>8</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E113" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F113" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G113" s="51" t="n">
@@ -9937,13 +9974,13 @@
         <v>9</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E114" s="50" t="n">
         <v>0.6</v>
       </c>
       <c r="F114" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G114" s="51" t="n">
@@ -9973,13 +10010,13 @@
         <v>9</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="E115" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F115" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G115" s="51" t="n">
@@ -10009,13 +10046,13 @@
         <v>9</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E116" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F116" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G116" s="51" t="n">
@@ -10045,13 +10082,13 @@
         <v>9</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E117" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F117" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G117" s="51" t="n">
@@ -10081,13 +10118,13 @@
         <v>9</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E118" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F118" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G118" s="51" t="n">
@@ -10117,14 +10154,14 @@
         <v>9</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E119" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F119" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G119" s="51" t="n">
@@ -10154,13 +10191,13 @@
         <v>10</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E120" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F120" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G120" s="51" t="n">
@@ -10190,13 +10227,13 @@
         <v>10</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E121" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F121" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G121" s="51" t="n">
@@ -10226,7 +10263,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E122" s="50"/>
       <c r="F122" s="51"/>
@@ -10234,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I122" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -10256,7 +10293,7 @@
         <v>22</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E123" s="50"/>
       <c r="F123" s="51"/>
@@ -10286,7 +10323,7 @@
         <v>22</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E124" s="50"/>
       <c r="F124" s="51"/>
@@ -10316,7 +10353,7 @@
         <v>22</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E125" s="50"/>
       <c r="F125" s="51"/>
@@ -10346,7 +10383,7 @@
         <v>22</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E126" s="50"/>
       <c r="F126" s="51"/>
@@ -10376,7 +10413,7 @@
         <v>22</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E127" s="50"/>
       <c r="F127" s="51"/>
@@ -10406,7 +10443,7 @@
         <v>22</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E128" s="50"/>
       <c r="F128" s="51"/>
@@ -10414,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I128" s="7" t="n">
         <f aca="false">Narxlar!$C$61</f>
@@ -10430,7 +10467,7 @@
       <c r="B129" s="54"/>
       <c r="C129" s="54"/>
       <c r="D129" s="11" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E129" s="54"/>
       <c r="F129" s="54"/>
@@ -10467,13 +10504,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E132" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F132" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G132" s="51" t="n">
@@ -10503,13 +10540,13 @@
         <v>8</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E133" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F133" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G133" s="51" t="n">
@@ -10539,14 +10576,14 @@
         <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E134" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F134" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G134" s="51" t="n">
@@ -10576,13 +10613,13 @@
         <v>9</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E135" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F135" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G135" s="51" t="n">
@@ -10612,13 +10649,13 @@
         <v>9</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="E136" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F136" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G136" s="51" t="n">
@@ -10648,13 +10685,13 @@
         <v>9</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E137" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F137" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G137" s="51" t="n">
@@ -10684,13 +10721,13 @@
         <v>9</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E138" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F138" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G138" s="51" t="n">
@@ -10720,13 +10757,13 @@
         <v>9</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E139" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F139" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G139" s="51" t="n">
@@ -10756,14 +10793,14 @@
         <v>9</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E140" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F140" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G140" s="51" t="n">
@@ -10793,13 +10830,13 @@
         <v>10</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E141" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F141" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G141" s="51" t="n">
@@ -10829,13 +10866,13 @@
         <v>10</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E142" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F142" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G142" s="51" t="n">
@@ -10865,7 +10902,7 @@
         <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E143" s="50"/>
       <c r="F143" s="51"/>
@@ -10873,7 +10910,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I143" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -10895,7 +10932,7 @@
         <v>22</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E144" s="50"/>
       <c r="F144" s="51"/>
@@ -10925,7 +10962,7 @@
         <v>22</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E145" s="50"/>
       <c r="F145" s="51"/>
@@ -10955,7 +10992,7 @@
         <v>22</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E146" s="50"/>
       <c r="F146" s="51"/>
@@ -10985,7 +11022,7 @@
         <v>22</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E147" s="50"/>
       <c r="F147" s="51"/>
@@ -11015,7 +11052,7 @@
         <v>22</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E148" s="50"/>
       <c r="F148" s="51"/>
@@ -11023,7 +11060,7 @@
         <v>1</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I148" s="7" t="n">
         <f aca="false">Narxlar!$C$62</f>
@@ -11039,7 +11076,7 @@
       <c r="B149" s="54"/>
       <c r="C149" s="54"/>
       <c r="D149" s="11" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E149" s="54"/>
       <c r="F149" s="54"/>
@@ -11076,13 +11113,13 @@
         <v>8</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E152" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F152" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G152" s="51" t="n">
@@ -11112,13 +11149,13 @@
         <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E153" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F153" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G153" s="51" t="n">
@@ -11148,14 +11185,14 @@
         <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E154" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F154" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G154" s="51" t="n">
@@ -11185,13 +11222,13 @@
         <v>9</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E155" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F155" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G155" s="51" t="n">
@@ -11221,13 +11258,13 @@
         <v>9</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E156" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F156" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G156" s="51" t="n">
@@ -11257,13 +11294,13 @@
         <v>9</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E157" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F157" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G157" s="51" t="n">
@@ -11293,13 +11330,13 @@
         <v>9</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E158" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F158" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G158" s="51" t="n">
@@ -11329,13 +11366,13 @@
         <v>9</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E159" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F159" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G159" s="51" t="n">
@@ -11365,14 +11402,14 @@
         <v>9</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E160" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F160" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G160" s="51" t="n">
@@ -11402,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E161" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F161" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G161" s="51" t="n">
@@ -11438,13 +11475,13 @@
         <v>10</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E162" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F162" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G162" s="51" t="n">
@@ -11474,7 +11511,7 @@
         <v>13</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E163" s="50"/>
       <c r="F163" s="51"/>
@@ -11482,7 +11519,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I163" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11498,7 +11535,7 @@
       <c r="B164" s="54"/>
       <c r="C164" s="54"/>
       <c r="D164" s="11" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E164" s="54"/>
       <c r="F164" s="54"/>
@@ -11535,13 +11572,13 @@
         <v>8</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E167" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F167" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G167" s="51" t="n">
@@ -11571,13 +11608,13 @@
         <v>8</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E168" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F168" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G168" s="51" t="n">
@@ -11607,14 +11644,14 @@
         <v>8</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E169" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F169" s="31" t="n">
-        <f aca="false">Narxlar!$C$70</f>
+        <f aca="false">Narxlar!$C$72</f>
         <v>2.5</v>
       </c>
       <c r="G169" s="51" t="n">
@@ -11644,13 +11681,13 @@
         <v>9</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E170" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F170" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G170" s="51" t="n">
@@ -11680,13 +11717,13 @@
         <v>9</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E171" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F171" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G171" s="51" t="n">
@@ -11716,13 +11753,13 @@
         <v>9</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E172" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F172" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G172" s="51" t="n">
@@ -11752,13 +11789,13 @@
         <v>9</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E173" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F173" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G173" s="51" t="n">
@@ -11788,13 +11825,13 @@
         <v>9</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E174" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F174" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G174" s="51" t="n">
@@ -11824,14 +11861,14 @@
         <v>9</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E175" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F175" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G175" s="51" t="n">
@@ -11861,13 +11898,13 @@
         <v>10</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E176" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F176" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G176" s="51" t="n">
@@ -11897,13 +11934,13 @@
         <v>10</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E177" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F177" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G177" s="51" t="n">
@@ -11933,7 +11970,7 @@
         <v>13</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E178" s="50"/>
       <c r="F178" s="51"/>
@@ -11941,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I178" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11957,7 +11994,7 @@
       <c r="B179" s="54"/>
       <c r="C179" s="54"/>
       <c r="D179" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E179" s="54"/>
       <c r="F179" s="54"/>
@@ -11994,13 +12031,13 @@
         <v>10</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E182" s="50" t="n">
         <v>5.95</v>
       </c>
       <c r="F182" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G182" s="51" t="n">
@@ -12030,14 +12067,14 @@
         <v>10</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E183" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
+      </c>
+      <c r="F183" s="31" t="n">
         <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
-      </c>
-      <c r="F183" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
         <v>2.1</v>
       </c>
       <c r="G183" s="51" t="n">
@@ -12067,13 +12104,13 @@
         <v>10</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E184" s="50" t="n">
         <v>2.95</v>
       </c>
       <c r="F184" s="31" t="n">
-        <f aca="false">Narxlar!$C$75</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G184" s="51" t="n">
@@ -12103,7 +12140,7 @@
         <v>13</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E185" s="50"/>
       <c r="F185" s="51"/>
@@ -12111,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I185" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -12127,7 +12164,7 @@
       <c r="B186" s="54"/>
       <c r="C186" s="54"/>
       <c r="D186" s="11" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E186" s="54"/>
       <c r="F186" s="54"/>
@@ -12164,13 +12201,13 @@
         <v>9</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E189" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F189" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G189" s="51" t="n">
@@ -12200,13 +12237,13 @@
         <v>9</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E190" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F190" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G190" s="51" t="n">
@@ -12236,13 +12273,13 @@
         <v>9</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E191" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F191" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G191" s="51" t="n">
@@ -12272,13 +12309,13 @@
         <v>9</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E192" s="50" t="n">
         <v>0.55</v>
       </c>
       <c r="F192" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G192" s="51" t="n">
@@ -12308,13 +12345,13 @@
         <v>9</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E193" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F193" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G193" s="51" t="n">
@@ -12344,13 +12381,13 @@
         <v>9</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E194" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F194" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G194" s="51" t="n">
@@ -12380,13 +12417,13 @@
         <v>9</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E195" s="50" t="n">
         <v>5.9</v>
       </c>
       <c r="F195" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G195" s="51" t="n">
@@ -12416,13 +12453,13 @@
         <v>9</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E196" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F196" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G196" s="51" t="n">
@@ -12452,13 +12489,13 @@
         <v>9</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E197" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F197" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G197" s="51" t="n">
@@ -12488,13 +12525,13 @@
         <v>9</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E198" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F198" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G198" s="51" t="n">
@@ -12524,13 +12561,13 @@
         <v>9</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E199" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F199" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G199" s="51" t="n">
@@ -12560,13 +12597,13 @@
         <v>9</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E200" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F200" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G200" s="51" t="n">
@@ -12596,18 +12633,18 @@
         <v>9</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E201" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F201" s="31" t="n">
         <f aca="false">Narxlar!$C$71</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G201" s="51" t="n">
         <f aca="false">E201*F201</f>
-        <v>1.15</v>
+        <v>4.025</v>
       </c>
       <c r="H201" s="5" t="s">
         <v>157</v>
@@ -12618,7 +12655,7 @@
       </c>
       <c r="J201" s="53" t="n">
         <f aca="false">G201*I201</f>
-        <v>13.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12632,14 +12669,14 @@
         <v>9</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E202" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F202" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G202" s="51" t="n">
@@ -12669,14 +12706,14 @@
         <v>9</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E203" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F203" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G203" s="51" t="n">
@@ -12706,14 +12743,14 @@
         <v>9</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E204" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F204" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G204" s="51" t="n">
@@ -12743,14 +12780,14 @@
         <v>9</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E205" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F205" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G205" s="51" t="n">
@@ -12780,14 +12817,14 @@
         <v>9</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E206" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F206" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G206" s="51" t="n">
@@ -12817,7 +12854,7 @@
         <v>13</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E207" s="50"/>
       <c r="F207" s="51"/>
@@ -12825,7 +12862,7 @@
         <v>1</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I207" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -12847,7 +12884,7 @@
         <v>23</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E208" s="50"/>
       <c r="F208" s="51"/>
@@ -12877,7 +12914,7 @@
         <v>23</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E209" s="50"/>
       <c r="F209" s="51"/>
@@ -12901,7 +12938,7 @@
       <c r="B210" s="54"/>
       <c r="C210" s="54"/>
       <c r="D210" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E210" s="54"/>
       <c r="F210" s="54"/>
@@ -12910,7 +12947,7 @@
       <c r="I210" s="54"/>
       <c r="J210" s="12" t="n">
         <f aca="false">SUM(J189:J209)</f>
-        <v>1295.5</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12938,13 +12975,13 @@
         <v>9</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E213" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F213" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G213" s="51" t="n">
@@ -12974,13 +13011,13 @@
         <v>9</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E214" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F214" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G214" s="51" t="n">
@@ -13010,13 +13047,13 @@
         <v>9</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E215" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F215" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G215" s="51" t="n">
@@ -13046,13 +13083,13 @@
         <v>9</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E216" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F216" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G216" s="51" t="n">
@@ -13082,13 +13119,13 @@
         <v>9</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E217" s="50" t="n">
         <v>6.3</v>
       </c>
       <c r="F217" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G217" s="51" t="n">
@@ -13118,13 +13155,13 @@
         <v>9</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E218" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F218" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G218" s="51" t="n">
@@ -13154,13 +13191,13 @@
         <v>9</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E219" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F219" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G219" s="51" t="n">
@@ -13190,13 +13227,13 @@
         <v>9</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E220" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F220" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G220" s="51" t="n">
@@ -13226,13 +13263,13 @@
         <v>9</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E221" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F221" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G221" s="51" t="n">
@@ -13262,13 +13299,13 @@
         <v>9</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E222" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F222" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G222" s="51" t="n">
@@ -13298,13 +13335,13 @@
         <v>9</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E223" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F223" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G223" s="51" t="n">
@@ -13334,13 +13371,13 @@
         <v>9</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E224" s="50" t="n">
         <v>0.35</v>
       </c>
       <c r="F224" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G224" s="51" t="n">
@@ -13370,13 +13407,13 @@
         <v>9</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E225" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F225" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G225" s="51" t="n">
@@ -13406,14 +13443,14 @@
         <v>9</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E226" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F226" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G226" s="51" t="n">
@@ -13443,14 +13480,14 @@
         <v>9</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E227" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F227" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G227" s="51" t="n">
@@ -13480,14 +13517,14 @@
         <v>9</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E228" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F228" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G228" s="51" t="n">
@@ -13517,14 +13554,14 @@
         <v>9</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E229" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F229" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G229" s="51" t="n">
@@ -13554,14 +13591,14 @@
         <v>9</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E230" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F230" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G230" s="51" t="n">
@@ -13591,14 +13628,14 @@
         <v>9</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E231" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$76</f>
         <v>0.9</v>
       </c>
       <c r="F231" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$73</f>
         <v>1</v>
       </c>
       <c r="G231" s="51" t="n">
@@ -13628,7 +13665,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E232" s="50"/>
       <c r="F232" s="51"/>
@@ -13636,7 +13673,7 @@
         <v>1</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I232" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13658,7 +13695,7 @@
         <v>23</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E233" s="50"/>
       <c r="F233" s="51"/>
@@ -13688,7 +13725,7 @@
         <v>23</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E234" s="50"/>
       <c r="F234" s="51"/>
@@ -13712,7 +13749,7 @@
       <c r="B235" s="54"/>
       <c r="C235" s="54"/>
       <c r="D235" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E235" s="54"/>
       <c r="F235" s="54"/>
@@ -13749,13 +13786,13 @@
         <v>9</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E238" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F238" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G238" s="51" t="n">
@@ -13785,13 +13822,13 @@
         <v>9</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E239" s="50" t="n">
         <v>0.7</v>
       </c>
       <c r="F239" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G239" s="51" t="n">
@@ -13821,13 +13858,13 @@
         <v>9</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E240" s="50" t="n">
         <v>1.65</v>
       </c>
       <c r="F240" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G240" s="51" t="n">
@@ -13857,7 +13894,7 @@
         <v>13</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E241" s="50"/>
       <c r="F241" s="51"/>
@@ -13865,7 +13902,7 @@
         <v>1</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I241" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13881,7 +13918,7 @@
       <c r="B242" s="54"/>
       <c r="C242" s="54"/>
       <c r="D242" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E242" s="54"/>
       <c r="F242" s="54"/>
@@ -13918,13 +13955,13 @@
         <v>9</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E245" s="50" t="n">
         <v>2.6</v>
       </c>
       <c r="F245" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G245" s="51" t="n">
@@ -13948,7 +13985,7 @@
       <c r="B246" s="54"/>
       <c r="C246" s="54"/>
       <c r="D246" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E246" s="54"/>
       <c r="F246" s="54"/>
@@ -13985,7 +14022,7 @@
         <v>12</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E249" s="31" t="n">
         <f aca="false">Narxlar!$C$10</f>
@@ -14013,7 +14050,7 @@
       <c r="B250" s="54"/>
       <c r="C250" s="54"/>
       <c r="D250" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E250" s="54"/>
       <c r="F250" s="54"/>
@@ -14081,7 +14118,7 @@
         <v>14</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E254" s="50"/>
       <c r="F254" s="51"/>
@@ -14142,7 +14179,7 @@
         <v>14</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E256" s="50"/>
       <c r="F256" s="51"/>
@@ -14150,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I256" s="7" t="n">
         <f aca="false">Narxlar!$C$17</f>
@@ -14172,7 +14209,7 @@
         <v>15</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E257" s="50"/>
       <c r="F257" s="51"/>
@@ -14180,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I257" s="7" t="n">
         <f aca="false">Narxlar!$C$18</f>
@@ -14202,7 +14239,7 @@
         <v>16</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E258" s="50"/>
       <c r="F258" s="51"/>
@@ -14233,7 +14270,7 @@
         <v>17</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E259" s="50"/>
       <c r="F259" s="51"/>
@@ -14241,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I259" s="7" t="n">
         <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
@@ -14263,13 +14300,13 @@
         <v>18</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E260" s="50" t="n">
         <v>1.1</v>
       </c>
       <c r="F260" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G260" s="51" t="n">
@@ -14299,13 +14336,13 @@
         <v>18</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E261" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F261" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G261" s="51" t="n">
@@ -14335,13 +14372,13 @@
         <v>18</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E262" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F262" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G262" s="51" t="n">
@@ -14371,13 +14408,13 @@
         <v>18</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E263" s="50" t="n">
         <v>0.75</v>
       </c>
       <c r="F263" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G263" s="51" t="n">
@@ -14407,13 +14444,13 @@
         <v>18</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E264" s="50" t="n">
         <v>3.4</v>
       </c>
       <c r="F264" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G264" s="51" t="n">
@@ -14443,13 +14480,13 @@
         <v>18</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E265" s="50" t="n">
         <v>4.2</v>
       </c>
       <c r="F265" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G265" s="51" t="n">
@@ -14479,13 +14516,13 @@
         <v>18</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E266" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F266" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G266" s="51" t="n">
@@ -14515,13 +14552,13 @@
         <v>18</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E267" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F267" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G267" s="51" t="n">
@@ -14551,13 +14588,13 @@
         <v>18</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E268" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F268" s="31" t="n">
-        <f aca="false">Narxlar!$C$69</f>
+        <f aca="false">Narxlar!$C$71</f>
         <v>3.5</v>
       </c>
       <c r="G268" s="51" t="n">
@@ -14587,7 +14624,7 @@
         <v>18</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E269" s="50"/>
       <c r="F269" s="51"/>
@@ -14595,7 +14632,7 @@
         <v>1</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I269" s="7" t="n">
         <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
@@ -14617,7 +14654,7 @@
         <v>21</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E270" s="50"/>
       <c r="F270" s="51"/>
@@ -14625,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I270" s="7" t="n">
         <f aca="false">Narxlar!$C$52</f>
@@ -14647,7 +14684,7 @@
         <v>21</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E271" s="50"/>
       <c r="F271" s="51"/>
@@ -14655,7 +14692,7 @@
         <v>1</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I271" s="7" t="n">
         <f aca="false">Narxlar!$C$53</f>
@@ -14671,7 +14708,7 @@
       <c r="B272" s="54"/>
       <c r="C272" s="54"/>
       <c r="D272" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E272" s="54"/>
       <c r="F272" s="54"/>
@@ -14708,13 +14745,13 @@
         <v>10</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E275" s="50" t="n">
         <v>5.45</v>
       </c>
       <c r="F275" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G275" s="51" t="n">
@@ -14744,13 +14781,13 @@
         <v>10</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E276" s="50" t="n">
         <v>5.45</v>
       </c>
       <c r="F276" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G276" s="51" t="n">
@@ -14780,13 +14817,13 @@
         <v>10</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E277" s="50" t="n">
         <v>8.6</v>
       </c>
       <c r="F277" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G277" s="51" t="n">
@@ -14816,14 +14853,14 @@
         <v>10</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E278" s="31" t="n">
+        <f aca="false">Narxlar!$C$76</f>
+        <v>0.9</v>
+      </c>
+      <c r="F278" s="31" t="n">
         <f aca="false">Narxlar!$C$74</f>
-        <v>0.9</v>
-      </c>
-      <c r="F278" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
         <v>2.1</v>
       </c>
       <c r="G278" s="51" t="n">
@@ -14853,7 +14890,7 @@
         <v>11</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E279" s="50"/>
       <c r="F279" s="51"/>
@@ -14883,7 +14920,7 @@
         <v>21</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E280" s="50"/>
       <c r="F280" s="51"/>
@@ -14907,7 +14944,7 @@
       <c r="B281" s="54"/>
       <c r="C281" s="54"/>
       <c r="D281" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E281" s="54"/>
       <c r="F281" s="54"/>
@@ -14944,7 +14981,7 @@
         <v>19</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E284" s="50"/>
       <c r="F284" s="51"/>
@@ -14975,7 +15012,7 @@
         <v>19</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E285" s="50"/>
       <c r="F285" s="51"/>
@@ -15006,7 +15043,7 @@
         <v>19</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E286" s="50"/>
       <c r="F286" s="51"/>
@@ -15037,7 +15074,7 @@
         <v>19</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E287" s="50"/>
       <c r="F287" s="51"/>
@@ -15068,7 +15105,7 @@
         <v>19</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E288" s="50"/>
       <c r="F288" s="51"/>
@@ -15099,7 +15136,7 @@
         <v>19</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E289" s="50"/>
       <c r="F289" s="51"/>
@@ -15130,7 +15167,7 @@
         <v>19</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E290" s="50"/>
       <c r="F290" s="51"/>
@@ -15161,7 +15198,7 @@
         <v>19</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E291" s="50"/>
       <c r="F291" s="51"/>
@@ -15285,7 +15322,7 @@
         <v>19</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E295" s="50"/>
       <c r="F295" s="51"/>
@@ -15293,7 +15330,7 @@
         <v>1</v>
       </c>
       <c r="H295" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I295" s="7" t="n">
         <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
@@ -15315,7 +15352,7 @@
         <v>20</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E296" s="50"/>
       <c r="F296" s="51"/>
@@ -15346,7 +15383,7 @@
         <v>20</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E297" s="50"/>
       <c r="F297" s="51"/>
@@ -15377,7 +15414,7 @@
         <v>20</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E298" s="50"/>
       <c r="F298" s="51"/>
@@ -15408,7 +15445,7 @@
         <v>20</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E299" s="50"/>
       <c r="F299" s="51"/>
@@ -15433,7 +15470,7 @@
       <c r="B300" s="54"/>
       <c r="C300" s="54"/>
       <c r="D300" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E300" s="54"/>
       <c r="F300" s="54"/>
@@ -15450,7 +15487,7 @@
       <c r="B302" s="54"/>
       <c r="C302" s="54"/>
       <c r="D302" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E302" s="54"/>
       <c r="F302" s="54"/>
@@ -15458,8 +15495,8 @@
       <c r="H302" s="54"/>
       <c r="I302" s="54"/>
       <c r="J302" s="12" t="n">
-        <f aca="false">J12+J25+J37+J48+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J242+J246+J250+J272+J281+J300</f>
-        <v>67165.3055882353</v>
+        <f aca="false">J13+J26+J38+J49+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J242+J246+J250+J272+J281+J300</f>
+        <v>67576.1805882353</v>
       </c>
     </row>
   </sheetData>
